--- a/survey_templates/045_nail_polish_purchase_behavior_survey--survey_templates.xlsx
+++ b/survey_templates/045_nail_polish_purchase_behavior_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sally_hansen</t>
+          <t>lvmh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sally Hansen</t>
+          <t>LVMH</t>
         </is>
       </c>
     </row>
@@ -939,29 +939,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lvmh</t>
+          <t>deborah_lippmann</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LVMH</t>
+          <t>Deborah Lippmann</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>preferred_brand_choices</t>
+          <t>color_choice_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>deborah_lippmann</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Deborah Lippmann</t>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>pink</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>pink</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>coral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>pink</t>
+          <t>coral</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>coral</t>
+          <t>purple</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>coral</t>
+          <t>purple</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>blue</t>
         </is>
       </c>
     </row>
@@ -1041,29 +1041,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>yellow</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>yellow</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>color_choice_choices</t>
+          <t>price_range_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yellow</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1075,29 +1075,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>price_range_choices</t>
+          <t>nail_polish_type_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>gel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>gel</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gel</t>
+          <t>cream</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>gel</t>
+          <t>cream</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>cream</t>
+          <t>mousse</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cream</t>
+          <t>mousse</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mousse</t>
+          <t>dipping</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mousse</t>
+          <t>dipping</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dipping</t>
+          <t>brush</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dipping</t>
+          <t>brush</t>
         </is>
       </c>
     </row>
@@ -1177,29 +1177,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>brush</t>
+          <t>sponge</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>brush</t>
+          <t>sponge</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>nail_polish_type_choices</t>
+          <t>nail_polish_reason_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sponge</t>
+          <t>want_to_look_good</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sponge</t>
+          <t>want to look good</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>want_to_look_good</t>
+          <t>want_to_feel_good</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>want to look good</t>
+          <t>want to feel good</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>want_to_feel_good</t>
+          <t>want_to_feel_confident</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>want to feel good</t>
+          <t>want to feel confident</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>want_to_feel_confident</t>
+          <t>want_to_express_myself</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>want to feel confident</t>
+          <t>want to express myself</t>
         </is>
       </c>
     </row>
@@ -1262,27 +1262,10 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>want_to_express_myself</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>want to express myself</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>nail_polish_reason_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>other</t>
         </is>
